--- a/testCases/Test_Automation_Practice_Test_Cases.xlsx
+++ b/testCases/Test_Automation_Practice_Test_Cases.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14640" windowHeight="8364"/>
+    <workbookView windowWidth="23040" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="114">
   <si>
     <t>Test ID</t>
   </si>
@@ -113,41 +113,62 @@
     <t>TC-004</t>
   </si>
   <si>
-    <t>Mouse Hover</t>
-  </si>
-  <si>
-    <t>Verify that hovering over the Point Me button displays the dropdown options</t>
-  </si>
-  <si>
-    <t>1. Hover over Point Me</t>
-  </si>
-  <si>
-    <t>The dropdown menu becomes visible and displays options such as Mobiles and Laptops</t>
+    <t>Mouse Hover - Select Option</t>
+  </si>
+  <si>
+    <t>Verify that hovering over the Point Me button displays the dropdown and allows an option to be selected</t>
+  </si>
+  <si>
+    <r>
+      <t>1. Hover over the Point Me button</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Merriweather"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Merriweather"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2. Verify that the dropdown is displayed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Merriweather"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Merriweather"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3. Select Mobiles</t>
+    </r>
+  </si>
+  <si>
+    <t>Mobiles</t>
+  </si>
+  <si>
+    <t>The dropdown is displayed with options such as Mobiles and Laptops. The Mobiles option can be selected and the dropdown closes.</t>
   </si>
   <si>
     <t>TC-005</t>
-  </si>
-  <si>
-    <t>Mouse Hover - Select Option</t>
-  </si>
-  <si>
-    <t>Dropdown is displayed</t>
-  </si>
-  <si>
-    <t>Verify that an option can be selected from the hover menu</t>
-  </si>
-  <si>
-    <t>1. Hover over Point Me 
-2. Select Mobiles</t>
-  </si>
-  <si>
-    <t>Mobiles</t>
-  </si>
-  <si>
-    <t>The Mobiles option is selected and the dropdown closes</t>
-  </si>
-  <si>
-    <t>TC-006</t>
   </si>
   <si>
     <t>Double Click</t>
@@ -163,7 +184,7 @@
     <t>The value in Field 2 matches the value in Field 1</t>
   </si>
   <si>
-    <t>TC-007</t>
+    <t>TC-006</t>
   </si>
   <si>
     <t>Drag and Drop</t>
@@ -179,7 +200,7 @@
     <t>The draggable element is successfully dropped into the target container</t>
   </si>
   <si>
-    <t>TC-008</t>
+    <t>TC-007</t>
   </si>
   <si>
     <t>Single File Upload</t>
@@ -198,7 +219,7 @@
     <t>The selected file is uploaded successfully and the expected upload result is displayed</t>
   </si>
   <si>
-    <t>TC-009</t>
+    <t>TC-008</t>
   </si>
   <si>
     <t>Multiple File Upload</t>
@@ -217,7 +238,7 @@
     <t>The selected files are uploaded successfully and the expected upload result is displayed</t>
   </si>
   <si>
-    <t>TC-010</t>
+    <t>TC-009</t>
   </si>
   <si>
     <t>Wikipedia Search</t>
@@ -236,7 +257,7 @@
     <t>Wikipedia search results are displayed and the results contain the searched term</t>
   </si>
   <si>
-    <t>TC-011</t>
+    <t>TC-010</t>
   </si>
   <si>
     <t>Form Input Fields</t>
@@ -288,7 +309,7 @@
     <t>The entered information is displayed correctly in the respective fields</t>
   </si>
   <si>
-    <t>TC-012</t>
+    <t>TC-011</t>
   </si>
   <si>
     <t>Gender and Days Selection</t>
@@ -310,7 +331,7 @@
     <t>Female and the selected days are checked</t>
   </si>
   <si>
-    <t>TC-013</t>
+    <t>TC-012</t>
   </si>
   <si>
     <t>Dropdown Selection</t>
@@ -330,22 +351,22 @@
     <t>The selected values are displayed/selected in the respective dropdowns</t>
   </si>
   <si>
+    <t>TC-013</t>
+  </si>
+  <si>
+    <t>First Date Picker</t>
+  </si>
+  <si>
+    <t>Verify that a date can be entered using the first date picker</t>
+  </si>
+  <si>
+    <t>1. Enter/select the date</t>
+  </si>
+  <si>
+    <t>The selected date is displayed in the date field</t>
+  </si>
+  <si>
     <t>TC-014</t>
-  </si>
-  <si>
-    <t>First Date Picker</t>
-  </si>
-  <si>
-    <t>Verify that a date can be entered using the first date picker</t>
-  </si>
-  <si>
-    <t>1. Enter/select the date</t>
-  </si>
-  <si>
-    <t>The selected date is displayed in the date field</t>
-  </si>
-  <si>
-    <t>TC-015</t>
   </si>
   <si>
     <t>Second Date Picker</t>
@@ -360,7 +381,7 @@
 4. Select day</t>
   </si>
   <si>
-    <t>TC-016</t>
+    <t>TC-015</t>
   </si>
   <si>
     <t>Date Range</t>
@@ -380,7 +401,7 @@
     <t>The selected dates are accepted and the calculated number of days is displayed</t>
   </si>
   <si>
-    <t>TC-017</t>
+    <t>TC-016</t>
   </si>
   <si>
     <t>Verify Book Price</t>
@@ -404,7 +425,7 @@
     <t>The price displayed for Master In Selenium should be 3000.</t>
   </si>
   <si>
-    <t>TC-018</t>
+    <t>TC-017</t>
   </si>
   <si>
     <t>Verify Browser Metrics</t>
@@ -427,7 +448,7 @@
     <t>The Chrome CPU (%) value in the table should match the corresponding displayed CPU value.</t>
   </si>
   <si>
-    <t>TC-019</t>
+    <t>TC-018</t>
   </si>
   <si>
     <t>Select Product from Pagination Table</t>
@@ -463,7 +484,7 @@
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -481,6 +502,12 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="Merriweather"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="Merriweather"/>
       <charset val="134"/>
     </font>
@@ -855,12 +882,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -964,152 +1006,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1120,7 +1162,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="58" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1604,7 +1655,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr defaultColWidth="12.6296296296296" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1732,38 +1783,57 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" ht="42.75" customHeight="1" spans="1:26">
-      <c r="A5" s="3" t="s">
+    <row r="5" ht="71" customHeight="1" spans="1:26">
+      <c r="A5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>30</v>
       </c>
+      <c r="G5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="6"/>
+      <c r="T5" s="6"/>
+      <c r="U5" s="6"/>
+      <c r="V5" s="6"/>
+      <c r="W5" s="6"/>
+      <c r="X5" s="6"/>
+      <c r="Y5" s="6"/>
+      <c r="Z5" s="6"/>
     </row>
-    <row r="6" ht="42.75" customHeight="1" spans="1:26">
-      <c r="A6" s="3" t="s">
-        <v>31</v>
+    <row r="6" ht="54" customHeight="1" spans="1:26">
+      <c r="A6" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>34</v>
@@ -1772,60 +1842,60 @@
         <v>35</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="3" t="s">
+    </row>
+    <row r="7" ht="44.25" customHeight="1" spans="1:26">
+      <c r="A7" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="7" ht="54" customHeight="1" spans="1:26">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>13</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" ht="51" customHeight="1" spans="1:26">
+      <c r="A8" s="4" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="8" ht="44.25" customHeight="1" spans="1:26">
-      <c r="A8" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="9" ht="51" customHeight="1" spans="1:26">
-      <c r="A9" s="3" t="s">
+    <row r="9" ht="40.5" customHeight="1" spans="1:26">
+      <c r="A9" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -1847,8 +1917,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" ht="40.5" customHeight="1" spans="1:26">
-      <c r="A10" s="3" t="s">
+    <row r="10" ht="42.75" customHeight="1" spans="1:26">
+      <c r="A10" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -1870,38 +1940,38 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" ht="42.75" customHeight="1" spans="1:26">
-      <c r="A11" s="3" t="s">
+    <row r="11" ht="73" customHeight="1" spans="1:26">
+      <c r="A11" s="4" t="s">
         <v>60</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1" spans="1:26">
+      <c r="A12" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" ht="73" customHeight="1" spans="1:26">
-      <c r="A12" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>69</v>
@@ -1909,22 +1979,22 @@
       <c r="E12" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>71</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="13" ht="48" customHeight="1" spans="1:26">
-      <c r="A13" s="3" t="s">
+    <row r="13" ht="41.25" customHeight="1" spans="1:26">
+      <c r="A13" s="4" t="s">
         <v>73</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>74</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>75</v>
@@ -1939,15 +2009,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" ht="41.25" customHeight="1" spans="1:26">
-      <c r="A14" s="3" t="s">
+    <row r="14" ht="46.5" customHeight="1" spans="1:26">
+      <c r="A14" s="4" t="s">
         <v>79</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>80</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>81</v>
@@ -1955,91 +2025,91 @@
       <c r="E14" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="8">
+        <v>46376</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G14" s="3" t="s">
+    </row>
+    <row r="15" ht="57" customHeight="1" spans="1:26">
+      <c r="A15" s="4" t="s">
         <v>84</v>
       </c>
+      <c r="B15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" s="9">
+        <v>46914</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>83</v>
+      </c>
     </row>
-    <row r="15" ht="46.5" customHeight="1" spans="1:26">
-      <c r="A15" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E15" s="3" t="s">
+    <row r="16" ht="42.75" customHeight="1" spans="1:26">
+      <c r="A16" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="F15" s="5">
-        <v>46376</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="B16" s="3" t="s">
         <v>89</v>
       </c>
+      <c r="C16" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>93</v>
+      </c>
     </row>
-    <row r="16" ht="57" customHeight="1" spans="1:26">
-      <c r="A16" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F16" s="6">
-        <v>46914</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" ht="42.75" customHeight="1" spans="1:7">
-      <c r="A17" s="3" t="s">
+    <row r="17" ht="44.25" customHeight="1" spans="1:7">
+      <c r="A17" s="4" t="s">
         <v>94</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>95</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" ht="79.5" customHeight="1" spans="1:7">
+      <c r="A18" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="18" ht="44.25" customHeight="1" spans="1:7">
-      <c r="A18" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>103</v>
@@ -2054,55 +2124,32 @@
         <v>106</v>
       </c>
     </row>
-    <row r="19" ht="79.5" customHeight="1" spans="1:7">
-      <c r="A19" s="3" t="s">
+    <row r="19" ht="87.75" customHeight="1" spans="1:7">
+      <c r="A19" s="4" t="s">
         <v>107</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>108</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="20" ht="87.75" customHeight="1" spans="1:7">
-      <c r="A20" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>119</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F12" r:id="rId1" display="Name: Zainab Abbas&#10;Email: zainababbas078@gmail.com&#10;Phone: 7523884910&#10;Address: 221 Baker Street, London NW1 6XE, United Kingdom"/>
+    <hyperlink ref="F11" r:id="rId1" display="Name: Zainab Abbas&#10;Email: zainababbas078@gmail.com&#10;Phone: 7523884910&#10;Address: 221 Baker Street, London NW1 6XE, United Kingdom"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
